--- a/data/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ27"/>
+  <dimension ref="A1:AJ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3712,8 +3712,962 @@
       <c r="AI27" s="2" t="inlineStr"/>
       <c r="AJ27" s="2" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>3afbf086a69f4a1f</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>66902</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0.558818</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0.539171</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>0.019647</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:09.199778Z</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/lol.xlsx;original_pick_id=3afbf086a69f4a1f;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr"/>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="2" t="inlineStr"/>
+      <c r="AH28" s="2" t="inlineStr"/>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>bc54b79b21264c05</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>66955</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0.592731</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0.659864</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>-0.067133</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:09.700659Z</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:15:00Z</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/lol.xlsx;original_pick_id=bc54b79b21264c05;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr"/>
+      <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AG29" s="2" t="inlineStr"/>
+      <c r="AH29" s="2" t="inlineStr"/>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>dae0495990e943f3</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>67492</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0.634473</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0.690402</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>-0.055929</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:11.750256Z</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/lol.xlsx;original_pick_id=dae0495990e943f3;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr"/>
+      <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>c3c74c8064844b1e</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>67491</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0.535770</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0.590164</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>-0.054394</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:12.301759Z</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/lol.xlsx;original_pick_id=c3c74c8064844b1e;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr"/>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AG31" s="2" t="inlineStr"/>
+      <c r="AH31" s="2" t="inlineStr"/>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>1f67cd97fc1f4d6c</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>0.703159</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0.690402</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>0.012757</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:12.813283Z</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/lol.xlsx;original_pick_id=1f67cd97fc1f4d6c;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr"/>
+      <c r="AE32" s="2" t="inlineStr"/>
+      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AG32" s="2" t="inlineStr"/>
+      <c r="AH32" s="2" t="inlineStr"/>
+      <c r="AI32" s="2" t="inlineStr"/>
+      <c r="AJ32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>48c53315f7064d79</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>0.746312</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0.619772</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>0.126540</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:13.406755Z</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/lol.xlsx;original_pick_id=48c53315f7064d79;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr"/>
+      <c r="AE33" s="2" t="inlineStr"/>
+      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AG33" s="2" t="inlineStr"/>
+      <c r="AH33" s="2" t="inlineStr"/>
+      <c r="AI33" s="2" t="inlineStr"/>
+      <c r="AJ33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>8dccf8d14155413d</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>0.746640</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0.699700</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>0.046940</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:13.923521Z</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/lol.xlsx;original_pick_id=8dccf8d14155413d;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr"/>
+      <c r="AE34" s="2" t="inlineStr"/>
+      <c r="AF34" s="2" t="inlineStr"/>
+      <c r="AG34" s="2" t="inlineStr"/>
+      <c r="AH34" s="2" t="inlineStr"/>
+      <c r="AI34" s="2" t="inlineStr"/>
+      <c r="AJ34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>754060c98b474189</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>0.649674</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>0.590164</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>0.059510</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:17.539022Z</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/lol.xlsx;original_pick_id=754060c98b474189;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr"/>
+      <c r="AE35" s="2" t="inlineStr"/>
+      <c r="AF35" s="2" t="inlineStr"/>
+      <c r="AG35" s="2" t="inlineStr"/>
+      <c r="AH35" s="2" t="inlineStr"/>
+      <c r="AI35" s="2" t="inlineStr"/>
+      <c r="AJ35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>b6d34c8bb890474f</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>4ef0b19fe97fa070abfaae40ffb41addfe8947e35583480b0b6feebe14b9f7ac</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>68011</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>0.501936</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0.559471</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>-0.057535</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:19.046288Z</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/lol.xlsx;original_pick_id=b6d34c8bb890474f;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="inlineStr"/>
+      <c r="AG36" s="2" t="inlineStr"/>
+      <c r="AH36" s="2" t="inlineStr"/>
+      <c r="AI36" s="2" t="inlineStr"/>
+      <c r="AJ36" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ27"/>
+  <autoFilter ref="A1:AJ36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ36"/>
+  <dimension ref="A1:AJ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4666,8 +4666,1436 @@
       <c r="AI36" s="2" t="inlineStr"/>
       <c r="AJ36" s="2" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>105f1d29f87145fe</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>ce2799e81af8529b307a74c160b17aa30970ae747db3a1beff420e3fd39f3e8c</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>67491</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>0.536074</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>-0.05408993442622945</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:24.266645Z</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr"/>
+      <c r="AE37" s="2" t="inlineStr"/>
+      <c r="AF37" s="2" t="inlineStr"/>
+      <c r="AG37" s="2" t="inlineStr"/>
+      <c r="AH37" s="2" t="inlineStr"/>
+      <c r="AI37" s="2" t="inlineStr"/>
+      <c r="AJ37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>53ce241a17164223</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>ce2799e81af8529b307a74c160b17aa30970ae747db3a1beff420e3fd39f3e8c</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>67492</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>0.634708</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>-0.05569447678018569</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:24.776615Z</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr"/>
+      <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AG38" s="2" t="inlineStr"/>
+      <c r="AH38" s="2" t="inlineStr"/>
+      <c r="AI38" s="2" t="inlineStr"/>
+      <c r="AJ38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>8ee5ef5eba4a4375</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>ce2799e81af8529b307a74c160b17aa30970ae747db3a1beff420e3fd39f3e8c</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>0.70331</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>0.012907523219814254</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:25.287120Z</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr"/>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr"/>
+      <c r="AE39" s="2" t="inlineStr"/>
+      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AG39" s="2" t="inlineStr"/>
+      <c r="AH39" s="2" t="inlineStr"/>
+      <c r="AI39" s="2" t="inlineStr"/>
+      <c r="AJ39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>df8cf65f396444f5</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>ce2799e81af8529b307a74c160b17aa30970ae747db3a1beff420e3fd39f3e8c</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>0.746406</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>0.13703100000000001</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:25.777893Z</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr"/>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr"/>
+      <c r="AE40" s="2" t="inlineStr"/>
+      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AG40" s="2" t="inlineStr"/>
+      <c r="AH40" s="2" t="inlineStr"/>
+      <c r="AI40" s="2" t="inlineStr"/>
+      <c r="AJ40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>0e63612b087e44d4</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>ce2799e81af8529b307a74c160b17aa30970ae747db3a1beff420e3fd39f3e8c</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>0.746125</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>0.04642530030030034</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:26.282734Z</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr"/>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr"/>
+      <c r="AE41" s="2" t="inlineStr"/>
+      <c r="AF41" s="2" t="inlineStr"/>
+      <c r="AG41" s="2" t="inlineStr"/>
+      <c r="AH41" s="2" t="inlineStr"/>
+      <c r="AI41" s="2" t="inlineStr"/>
+      <c r="AJ41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>7b5f46d4b16847c2</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>ce2799e81af8529b307a74c160b17aa30970ae747db3a1beff420e3fd39f3e8c</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>0.649195</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0.05903106557377047</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:29.638928Z</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr"/>
+      <c r="AE42" s="2" t="inlineStr"/>
+      <c r="AF42" s="2" t="inlineStr"/>
+      <c r="AG42" s="2" t="inlineStr"/>
+      <c r="AH42" s="2" t="inlineStr"/>
+      <c r="AI42" s="2" t="inlineStr"/>
+      <c r="AJ42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>923641f034344c34</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>ce2799e81af8529b307a74c160b17aa30970ae747db3a1beff420e3fd39f3e8c</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>68011</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>0.502316</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>-0.007487921568627431</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:31.198418Z</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr"/>
+      <c r="AE43" s="2" t="inlineStr"/>
+      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AG43" s="2" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr"/>
+      <c r="AI43" s="2" t="inlineStr"/>
+      <c r="AJ43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>c96e6e3f63c34892</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>67491</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0.536074</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>-0.05408993442622945</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:16.992475Z</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr"/>
+      <c r="AE44" s="2" t="inlineStr"/>
+      <c r="AF44" s="2" t="inlineStr"/>
+      <c r="AG44" s="2" t="inlineStr"/>
+      <c r="AH44" s="2" t="inlineStr"/>
+      <c r="AI44" s="2" t="inlineStr"/>
+      <c r="AJ44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>a99677ba1f56479f</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>67492</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>0.634708</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>-0.05569447678018569</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:17.534127Z</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr"/>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr"/>
+      <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="2" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr"/>
+      <c r="AI45" s="2" t="inlineStr"/>
+      <c r="AJ45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>b329ea2a83be4efc</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>0.70331</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>0.012907523219814254</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:18.085863Z</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr"/>
+      <c r="AE46" s="2" t="inlineStr"/>
+      <c r="AF46" s="2" t="inlineStr"/>
+      <c r="AG46" s="2" t="inlineStr"/>
+      <c r="AH46" s="2" t="inlineStr"/>
+      <c r="AI46" s="2" t="inlineStr"/>
+      <c r="AJ46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>b332716e59f344ed</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>0.746406</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>0.13703100000000001</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:18.584911Z</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr"/>
+      <c r="W47" s="2" t="inlineStr"/>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr"/>
+      <c r="AE47" s="2" t="inlineStr"/>
+      <c r="AF47" s="2" t="inlineStr"/>
+      <c r="AG47" s="2" t="inlineStr"/>
+      <c r="AH47" s="2" t="inlineStr"/>
+      <c r="AI47" s="2" t="inlineStr"/>
+      <c r="AJ47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>8eeab2d15aaf4938</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>0.746125</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>0.04642530030030034</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:19.163906Z</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr"/>
+      <c r="W48" s="2" t="inlineStr"/>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr"/>
+      <c r="AE48" s="2" t="inlineStr"/>
+      <c r="AF48" s="2" t="inlineStr"/>
+      <c r="AG48" s="2" t="inlineStr"/>
+      <c r="AH48" s="2" t="inlineStr"/>
+      <c r="AI48" s="2" t="inlineStr"/>
+      <c r="AJ48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>17333d9e0b384b9e</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>0.649195</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>0.05903106557377047</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:22.895388Z</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr"/>
+      <c r="W49" s="2" t="inlineStr"/>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr"/>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr"/>
+      <c r="AE49" s="2" t="inlineStr"/>
+      <c r="AF49" s="2" t="inlineStr"/>
+      <c r="AG49" s="2" t="inlineStr"/>
+      <c r="AH49" s="2" t="inlineStr"/>
+      <c r="AI49" s="2" t="inlineStr"/>
+      <c r="AJ49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>c15a8aa6796347d0</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>4f36308eb4ef5b33d9e3dc1ce778f2d60fa81380dd8ffa234241836516487e8e</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>68011</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>0.502316</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>-0.007487921568627431</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:24.464493Z</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr"/>
+      <c r="AE50" s="2" t="inlineStr"/>
+      <c r="AF50" s="2" t="inlineStr"/>
+      <c r="AG50" s="2" t="inlineStr"/>
+      <c r="AH50" s="2" t="inlineStr"/>
+      <c r="AI50" s="2" t="inlineStr"/>
+      <c r="AJ50" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ36"/>
+  <autoFilter ref="A1:AJ50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/model_ledgers/lol-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ50"/>
+  <dimension ref="A1:AJ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6094,8 +6094,824 @@
       <c r="AI50" s="2" t="inlineStr"/>
       <c r="AJ50" s="2" t="inlineStr"/>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>c5d51e5859794db6</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>67491</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>0.536074</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>-0.05408993442622945</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:08.792428Z</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr"/>
+      <c r="W51" s="2" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr"/>
+      <c r="AE51" s="2" t="inlineStr"/>
+      <c r="AF51" s="2" t="inlineStr"/>
+      <c r="AG51" s="2" t="inlineStr"/>
+      <c r="AH51" s="2" t="inlineStr"/>
+      <c r="AI51" s="2" t="inlineStr"/>
+      <c r="AJ51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>487afe819dfc47ee</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>67492</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>0.634708</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>-0.05569447678018569</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:09.253322Z</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr"/>
+      <c r="AE52" s="2" t="inlineStr"/>
+      <c r="AF52" s="2" t="inlineStr"/>
+      <c r="AG52" s="2" t="inlineStr"/>
+      <c r="AH52" s="2" t="inlineStr"/>
+      <c r="AI52" s="2" t="inlineStr"/>
+      <c r="AJ52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>444a1597d4d54443</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>67511</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>0.70331</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>0.012907523219814254</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:09.781954Z</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr"/>
+      <c r="W53" s="2" t="inlineStr"/>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr"/>
+      <c r="Z53" s="2" t="inlineStr"/>
+      <c r="AA53" s="2" t="inlineStr"/>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr"/>
+      <c r="AE53" s="2" t="inlineStr"/>
+      <c r="AF53" s="2" t="inlineStr"/>
+      <c r="AG53" s="2" t="inlineStr"/>
+      <c r="AH53" s="2" t="inlineStr"/>
+      <c r="AI53" s="2" t="inlineStr"/>
+      <c r="AJ53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>0a0552d47ba64a47</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>67515</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>0.746406</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>0.13703100000000001</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:10.279453Z</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr"/>
+      <c r="AE54" s="2" t="inlineStr"/>
+      <c r="AF54" s="2" t="inlineStr"/>
+      <c r="AG54" s="2" t="inlineStr"/>
+      <c r="AH54" s="2" t="inlineStr"/>
+      <c r="AI54" s="2" t="inlineStr"/>
+      <c r="AJ54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>5f54e7ec820c4d5d</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>67566</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>0.746125</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>0.04642530030030034</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:10.786284Z</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr"/>
+      <c r="W55" s="2" t="inlineStr"/>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr"/>
+      <c r="AE55" s="2" t="inlineStr"/>
+      <c r="AF55" s="2" t="inlineStr"/>
+      <c r="AG55" s="2" t="inlineStr"/>
+      <c r="AH55" s="2" t="inlineStr"/>
+      <c r="AI55" s="2" t="inlineStr"/>
+      <c r="AJ55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>d4bcf97cc83345cc</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>67937</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>0.649195</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>0.05903106557377047</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:14.243617Z</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="inlineStr"/>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr"/>
+      <c r="AE56" s="2" t="inlineStr"/>
+      <c r="AF56" s="2" t="inlineStr"/>
+      <c r="AG56" s="2" t="inlineStr"/>
+      <c r="AH56" s="2" t="inlineStr"/>
+      <c r="AI56" s="2" t="inlineStr"/>
+      <c r="AJ56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2a40c190253e4518</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>67938</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>0.62116</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>-0.07853969969969965</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:14.766196Z</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr"/>
+      <c r="W57" s="2" t="inlineStr"/>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr"/>
+      <c r="Z57" s="2" t="inlineStr"/>
+      <c r="AA57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr"/>
+      <c r="AE57" s="2" t="inlineStr"/>
+      <c r="AF57" s="2" t="inlineStr"/>
+      <c r="AG57" s="2" t="inlineStr"/>
+      <c r="AH57" s="2" t="inlineStr"/>
+      <c r="AI57" s="2" t="inlineStr"/>
+      <c r="AJ57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>051b96ef6ad44af2</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>9874c87288f5592f0598f78c78d9cd54fcbdac231ba8fa0dfab5378878942df2</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>68011</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>0.502316</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>-0.007487921568627431</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:15.724362Z</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr"/>
+      <c r="W58" s="2" t="inlineStr"/>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr"/>
+      <c r="AA58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr"/>
+      <c r="AE58" s="2" t="inlineStr"/>
+      <c r="AF58" s="2" t="inlineStr"/>
+      <c r="AG58" s="2" t="inlineStr"/>
+      <c r="AH58" s="2" t="inlineStr"/>
+      <c r="AI58" s="2" t="inlineStr"/>
+      <c r="AJ58" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ50"/>
+  <autoFilter ref="A1:AJ58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/lol-tiered-elo.xlsx
+++ b/data/model_ledgers/lol-tiered-elo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$217</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ202"/>
+  <dimension ref="A1:AJ217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -21638,8 +21638,1538 @@
       <c r="AI202" s="2" t="inlineStr"/>
       <c r="AJ202" s="2" t="inlineStr"/>
     </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>1a895f84b8554cff</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>698fbd14da7d032b3a980c8214767b8eb223167868cd2cea373258eb5e4ac7b4</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>76532</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K203" s="2" t="inlineStr"/>
+      <c r="L203" s="2" t="inlineStr">
+        <is>
+          <t>0.517262</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="inlineStr"/>
+      <c r="N203" s="2" t="inlineStr"/>
+      <c r="O203" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P203" s="2" t="inlineStr"/>
+      <c r="Q203" s="2" t="inlineStr">
+        <is>
+          <t>-0.05355345064377681</t>
+        </is>
+      </c>
+      <c r="R203" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:27.667035Z</t>
+        </is>
+      </c>
+      <c r="S203" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T203" s="2" t="inlineStr"/>
+      <c r="U203" s="2" t="inlineStr"/>
+      <c r="V203" s="2" t="inlineStr"/>
+      <c r="W203" s="2" t="inlineStr"/>
+      <c r="X203" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y203" s="2" t="inlineStr"/>
+      <c r="Z203" s="2" t="inlineStr"/>
+      <c r="AA203" s="2" t="inlineStr"/>
+      <c r="AB203" s="2" t="inlineStr"/>
+      <c r="AC203" s="2" t="inlineStr"/>
+      <c r="AD203" s="2" t="inlineStr"/>
+      <c r="AE203" s="2" t="inlineStr"/>
+      <c r="AF203" s="2" t="inlineStr"/>
+      <c r="AG203" s="2" t="inlineStr"/>
+      <c r="AH203" s="2" t="inlineStr"/>
+      <c r="AI203" s="2" t="inlineStr"/>
+      <c r="AJ203" s="2" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>cb1c7db172cf4039</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>698fbd14da7d032b3a980c8214767b8eb223167868cd2cea373258eb5e4ac7b4</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>76534</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>0.524795</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr"/>
+      <c r="N204" s="2" t="inlineStr"/>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P204" s="2" t="inlineStr"/>
+      <c r="Q204" s="2" t="inlineStr">
+        <is>
+          <t>-0.15571618210862614</t>
+        </is>
+      </c>
+      <c r="R204" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:29.444227Z</t>
+        </is>
+      </c>
+      <c r="S204" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T204" s="2" t="inlineStr"/>
+      <c r="U204" s="2" t="inlineStr"/>
+      <c r="V204" s="2" t="inlineStr"/>
+      <c r="W204" s="2" t="inlineStr"/>
+      <c r="X204" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y204" s="2" t="inlineStr"/>
+      <c r="Z204" s="2" t="inlineStr"/>
+      <c r="AA204" s="2" t="inlineStr"/>
+      <c r="AB204" s="2" t="inlineStr"/>
+      <c r="AC204" s="2" t="inlineStr"/>
+      <c r="AD204" s="2" t="inlineStr"/>
+      <c r="AE204" s="2" t="inlineStr"/>
+      <c r="AF204" s="2" t="inlineStr"/>
+      <c r="AG204" s="2" t="inlineStr"/>
+      <c r="AH204" s="2" t="inlineStr"/>
+      <c r="AI204" s="2" t="inlineStr"/>
+      <c r="AJ204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>cac9dbe884fa4379</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>698fbd14da7d032b3a980c8214767b8eb223167868cd2cea373258eb5e4ac7b4</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>79456</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K205" s="2" t="inlineStr"/>
+      <c r="L205" s="2" t="inlineStr">
+        <is>
+          <t>0.529083</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="inlineStr"/>
+      <c r="N205" s="2" t="inlineStr"/>
+      <c r="O205" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P205" s="2" t="inlineStr"/>
+      <c r="Q205" s="2" t="inlineStr">
+        <is>
+          <t>-0.09068886311787072</t>
+        </is>
+      </c>
+      <c r="R205" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:32.506392Z</t>
+        </is>
+      </c>
+      <c r="S205" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="T205" s="2" t="inlineStr"/>
+      <c r="U205" s="2" t="inlineStr"/>
+      <c r="V205" s="2" t="inlineStr"/>
+      <c r="W205" s="2" t="inlineStr"/>
+      <c r="X205" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y205" s="2" t="inlineStr"/>
+      <c r="Z205" s="2" t="inlineStr"/>
+      <c r="AA205" s="2" t="inlineStr"/>
+      <c r="AB205" s="2" t="inlineStr"/>
+      <c r="AC205" s="2" t="inlineStr"/>
+      <c r="AD205" s="2" t="inlineStr"/>
+      <c r="AE205" s="2" t="inlineStr"/>
+      <c r="AF205" s="2" t="inlineStr"/>
+      <c r="AG205" s="2" t="inlineStr"/>
+      <c r="AH205" s="2" t="inlineStr"/>
+      <c r="AI205" s="2" t="inlineStr"/>
+      <c r="AJ205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>104f564f8ef14c41</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>698fbd14da7d032b3a980c8214767b8eb223167868cd2cea373258eb5e4ac7b4</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>76941</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K206" s="2" t="inlineStr"/>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>0.52057</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr"/>
+      <c r="N206" s="2" t="inlineStr"/>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="inlineStr"/>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t>0.010766078431372561</t>
+        </is>
+      </c>
+      <c r="R206" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:33.295086Z</t>
+        </is>
+      </c>
+      <c r="S206" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T206" s="2" t="inlineStr"/>
+      <c r="U206" s="2" t="inlineStr"/>
+      <c r="V206" s="2" t="inlineStr"/>
+      <c r="W206" s="2" t="inlineStr"/>
+      <c r="X206" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y206" s="2" t="inlineStr"/>
+      <c r="Z206" s="2" t="inlineStr"/>
+      <c r="AA206" s="2" t="inlineStr"/>
+      <c r="AB206" s="2" t="inlineStr"/>
+      <c r="AC206" s="2" t="inlineStr"/>
+      <c r="AD206" s="2" t="inlineStr"/>
+      <c r="AE206" s="2" t="inlineStr"/>
+      <c r="AF206" s="2" t="inlineStr"/>
+      <c r="AG206" s="2" t="inlineStr"/>
+      <c r="AH206" s="2" t="inlineStr"/>
+      <c r="AI206" s="2" t="inlineStr"/>
+      <c r="AJ206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>7d187a985a0e4524</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>698fbd14da7d032b3a980c8214767b8eb223167868cd2cea373258eb5e4ac7b4</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>77049</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K207" s="2" t="inlineStr"/>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t>0.63125</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr"/>
+      <c r="N207" s="2" t="inlineStr"/>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P207" s="2" t="inlineStr"/>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t>-0.06844969969969972</t>
+        </is>
+      </c>
+      <c r="R207" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:34.860678Z</t>
+        </is>
+      </c>
+      <c r="S207" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T207" s="2" t="inlineStr"/>
+      <c r="U207" s="2" t="inlineStr"/>
+      <c r="V207" s="2" t="inlineStr"/>
+      <c r="W207" s="2" t="inlineStr"/>
+      <c r="X207" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y207" s="2" t="inlineStr"/>
+      <c r="Z207" s="2" t="inlineStr"/>
+      <c r="AA207" s="2" t="inlineStr"/>
+      <c r="AB207" s="2" t="inlineStr"/>
+      <c r="AC207" s="2" t="inlineStr"/>
+      <c r="AD207" s="2" t="inlineStr"/>
+      <c r="AE207" s="2" t="inlineStr"/>
+      <c r="AF207" s="2" t="inlineStr"/>
+      <c r="AG207" s="2" t="inlineStr"/>
+      <c r="AH207" s="2" t="inlineStr"/>
+      <c r="AI207" s="2" t="inlineStr"/>
+      <c r="AJ207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>f4d7471f360a49df</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>698fbd14da7d032b3a980c8214767b8eb223167868cd2cea373258eb5e4ac7b4</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>77155</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K208" s="2" t="inlineStr"/>
+      <c r="L208" s="2" t="inlineStr">
+        <is>
+          <t>0.543714</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="inlineStr"/>
+      <c r="N208" s="2" t="inlineStr"/>
+      <c r="O208" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P208" s="2" t="inlineStr"/>
+      <c r="Q208" s="2" t="inlineStr">
+        <is>
+          <t>0.10318536563876657</t>
+        </is>
+      </c>
+      <c r="R208" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:35.524238Z</t>
+        </is>
+      </c>
+      <c r="S208" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T208" s="2" t="inlineStr"/>
+      <c r="U208" s="2" t="inlineStr"/>
+      <c r="V208" s="2" t="inlineStr"/>
+      <c r="W208" s="2" t="inlineStr"/>
+      <c r="X208" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y208" s="2" t="inlineStr"/>
+      <c r="Z208" s="2" t="inlineStr"/>
+      <c r="AA208" s="2" t="inlineStr"/>
+      <c r="AB208" s="2" t="inlineStr"/>
+      <c r="AC208" s="2" t="inlineStr"/>
+      <c r="AD208" s="2" t="inlineStr"/>
+      <c r="AE208" s="2" t="inlineStr"/>
+      <c r="AF208" s="2" t="inlineStr"/>
+      <c r="AG208" s="2" t="inlineStr"/>
+      <c r="AH208" s="2" t="inlineStr"/>
+      <c r="AI208" s="2" t="inlineStr"/>
+      <c r="AJ208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>835c5f942f61434e</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>698fbd14da7d032b3a980c8214767b8eb223167868cd2cea373258eb5e4ac7b4</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>77160</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K209" s="2" t="inlineStr"/>
+      <c r="L209" s="2" t="inlineStr">
+        <is>
+          <t>0.519471</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="inlineStr"/>
+      <c r="N209" s="2" t="inlineStr"/>
+      <c r="O209" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P209" s="2" t="inlineStr"/>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
+          <t>-0.019699506912442377</t>
+        </is>
+      </c>
+      <c r="R209" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:37.204615Z</t>
+        </is>
+      </c>
+      <c r="S209" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:00:00Z</t>
+        </is>
+      </c>
+      <c r="T209" s="2" t="inlineStr"/>
+      <c r="U209" s="2" t="inlineStr"/>
+      <c r="V209" s="2" t="inlineStr"/>
+      <c r="W209" s="2" t="inlineStr"/>
+      <c r="X209" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y209" s="2" t="inlineStr"/>
+      <c r="Z209" s="2" t="inlineStr"/>
+      <c r="AA209" s="2" t="inlineStr"/>
+      <c r="AB209" s="2" t="inlineStr"/>
+      <c r="AC209" s="2" t="inlineStr"/>
+      <c r="AD209" s="2" t="inlineStr"/>
+      <c r="AE209" s="2" t="inlineStr"/>
+      <c r="AF209" s="2" t="inlineStr"/>
+      <c r="AG209" s="2" t="inlineStr"/>
+      <c r="AH209" s="2" t="inlineStr"/>
+      <c r="AI209" s="2" t="inlineStr"/>
+      <c r="AJ209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>80099fd4f2c74edf</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>698fbd14da7d032b3a980c8214767b8eb223167868cd2cea373258eb5e4ac7b4</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>77170</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K210" s="2" t="inlineStr"/>
+      <c r="L210" s="2" t="inlineStr">
+        <is>
+          <t>0.528933</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="inlineStr"/>
+      <c r="N210" s="2" t="inlineStr"/>
+      <c r="O210" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P210" s="2" t="inlineStr"/>
+      <c r="Q210" s="2" t="inlineStr">
+        <is>
+          <t>-0.0206165495495495</t>
+        </is>
+      </c>
+      <c r="R210" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:38.052595Z</t>
+        </is>
+      </c>
+      <c r="S210" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T210" s="2" t="inlineStr"/>
+      <c r="U210" s="2" t="inlineStr"/>
+      <c r="V210" s="2" t="inlineStr"/>
+      <c r="W210" s="2" t="inlineStr"/>
+      <c r="X210" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y210" s="2" t="inlineStr"/>
+      <c r="Z210" s="2" t="inlineStr"/>
+      <c r="AA210" s="2" t="inlineStr"/>
+      <c r="AB210" s="2" t="inlineStr"/>
+      <c r="AC210" s="2" t="inlineStr"/>
+      <c r="AD210" s="2" t="inlineStr"/>
+      <c r="AE210" s="2" t="inlineStr"/>
+      <c r="AF210" s="2" t="inlineStr"/>
+      <c r="AG210" s="2" t="inlineStr"/>
+      <c r="AH210" s="2" t="inlineStr"/>
+      <c r="AI210" s="2" t="inlineStr"/>
+      <c r="AJ210" s="2" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>1ec361358a6c4b6d</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>698fbd14da7d032b3a980c8214767b8eb223167868cd2cea373258eb5e4ac7b4</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>77184</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K211" s="2" t="inlineStr"/>
+      <c r="L211" s="2" t="inlineStr">
+        <is>
+          <t>0.506615</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="inlineStr"/>
+      <c r="N211" s="2" t="inlineStr"/>
+      <c r="O211" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P211" s="2" t="inlineStr"/>
+      <c r="Q211" s="2" t="inlineStr">
+        <is>
+          <t>-0.0528563656387665</t>
+        </is>
+      </c>
+      <c r="R211" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:38.855802Z</t>
+        </is>
+      </c>
+      <c r="S211" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T211" s="2" t="inlineStr"/>
+      <c r="U211" s="2" t="inlineStr"/>
+      <c r="V211" s="2" t="inlineStr"/>
+      <c r="W211" s="2" t="inlineStr"/>
+      <c r="X211" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y211" s="2" t="inlineStr"/>
+      <c r="Z211" s="2" t="inlineStr"/>
+      <c r="AA211" s="2" t="inlineStr"/>
+      <c r="AB211" s="2" t="inlineStr"/>
+      <c r="AC211" s="2" t="inlineStr"/>
+      <c r="AD211" s="2" t="inlineStr"/>
+      <c r="AE211" s="2" t="inlineStr"/>
+      <c r="AF211" s="2" t="inlineStr"/>
+      <c r="AG211" s="2" t="inlineStr"/>
+      <c r="AH211" s="2" t="inlineStr"/>
+      <c r="AI211" s="2" t="inlineStr"/>
+      <c r="AJ211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>1c3a33b08c704019</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>698fbd14da7d032b3a980c8214767b8eb223167868cd2cea373258eb5e4ac7b4</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>77199</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K212" s="2" t="inlineStr"/>
+      <c r="L212" s="2" t="inlineStr">
+        <is>
+          <t>0.550709</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="inlineStr"/>
+      <c r="N212" s="2" t="inlineStr"/>
+      <c r="O212" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P212" s="2" t="inlineStr"/>
+      <c r="Q212" s="2" t="inlineStr">
+        <is>
+          <t>0.11018036563876654</t>
+        </is>
+      </c>
+      <c r="R212" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:40.501608Z</t>
+        </is>
+      </c>
+      <c r="S212" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T212" s="2" t="inlineStr"/>
+      <c r="U212" s="2" t="inlineStr"/>
+      <c r="V212" s="2" t="inlineStr"/>
+      <c r="W212" s="2" t="inlineStr"/>
+      <c r="X212" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y212" s="2" t="inlineStr"/>
+      <c r="Z212" s="2" t="inlineStr"/>
+      <c r="AA212" s="2" t="inlineStr"/>
+      <c r="AB212" s="2" t="inlineStr"/>
+      <c r="AC212" s="2" t="inlineStr"/>
+      <c r="AD212" s="2" t="inlineStr"/>
+      <c r="AE212" s="2" t="inlineStr"/>
+      <c r="AF212" s="2" t="inlineStr"/>
+      <c r="AG212" s="2" t="inlineStr"/>
+      <c r="AH212" s="2" t="inlineStr"/>
+      <c r="AI212" s="2" t="inlineStr"/>
+      <c r="AJ212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>419de98ffd36474d</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>698fbd14da7d032b3a980c8214767b8eb223167868cd2cea373258eb5e4ac7b4</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>77533</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>0.598571</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="inlineStr"/>
+      <c r="N213" s="2" t="inlineStr"/>
+      <c r="O213" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P213" s="2" t="inlineStr"/>
+      <c r="Q213" s="2" t="inlineStr">
+        <is>
+          <t>-0.07139599669967</t>
+        </is>
+      </c>
+      <c r="R213" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:43.629485Z</t>
+        </is>
+      </c>
+      <c r="S213" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="T213" s="2" t="inlineStr"/>
+      <c r="U213" s="2" t="inlineStr"/>
+      <c r="V213" s="2" t="inlineStr"/>
+      <c r="W213" s="2" t="inlineStr"/>
+      <c r="X213" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y213" s="2" t="inlineStr"/>
+      <c r="Z213" s="2" t="inlineStr"/>
+      <c r="AA213" s="2" t="inlineStr"/>
+      <c r="AB213" s="2" t="inlineStr"/>
+      <c r="AC213" s="2" t="inlineStr"/>
+      <c r="AD213" s="2" t="inlineStr"/>
+      <c r="AE213" s="2" t="inlineStr"/>
+      <c r="AF213" s="2" t="inlineStr"/>
+      <c r="AG213" s="2" t="inlineStr"/>
+      <c r="AH213" s="2" t="inlineStr"/>
+      <c r="AI213" s="2" t="inlineStr"/>
+      <c r="AJ213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>6e448c402c1941d6</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>698fbd14da7d032b3a980c8214767b8eb223167868cd2cea373258eb5e4ac7b4</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>77534</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K214" s="2" t="inlineStr"/>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>0.618293</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="inlineStr"/>
+      <c r="N214" s="2" t="inlineStr"/>
+      <c r="O214" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P214" s="2" t="inlineStr"/>
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
+          <t>0.20845693442622948</t>
+        </is>
+      </c>
+      <c r="R214" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:46.185268Z</t>
+        </is>
+      </c>
+      <c r="S214" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="T214" s="2" t="inlineStr"/>
+      <c r="U214" s="2" t="inlineStr"/>
+      <c r="V214" s="2" t="inlineStr"/>
+      <c r="W214" s="2" t="inlineStr"/>
+      <c r="X214" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y214" s="2" t="inlineStr"/>
+      <c r="Z214" s="2" t="inlineStr"/>
+      <c r="AA214" s="2" t="inlineStr"/>
+      <c r="AB214" s="2" t="inlineStr"/>
+      <c r="AC214" s="2" t="inlineStr"/>
+      <c r="AD214" s="2" t="inlineStr"/>
+      <c r="AE214" s="2" t="inlineStr"/>
+      <c r="AF214" s="2" t="inlineStr"/>
+      <c r="AG214" s="2" t="inlineStr"/>
+      <c r="AH214" s="2" t="inlineStr"/>
+      <c r="AI214" s="2" t="inlineStr"/>
+      <c r="AJ214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>f8f7fe8e51a14187</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>698fbd14da7d032b3a980c8214767b8eb223167868cd2cea373258eb5e4ac7b4</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>77945</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K215" s="2" t="inlineStr"/>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>0.588508</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="inlineStr"/>
+      <c r="N215" s="2" t="inlineStr"/>
+      <c r="O215" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P215" s="2" t="inlineStr"/>
+      <c r="Q215" s="2" t="inlineStr">
+        <is>
+          <t>0.01769254935622322</t>
+        </is>
+      </c>
+      <c r="R215" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:51.498857Z</t>
+        </is>
+      </c>
+      <c r="S215" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="T215" s="2" t="inlineStr"/>
+      <c r="U215" s="2" t="inlineStr"/>
+      <c r="V215" s="2" t="inlineStr"/>
+      <c r="W215" s="2" t="inlineStr"/>
+      <c r="X215" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y215" s="2" t="inlineStr"/>
+      <c r="Z215" s="2" t="inlineStr"/>
+      <c r="AA215" s="2" t="inlineStr"/>
+      <c r="AB215" s="2" t="inlineStr"/>
+      <c r="AC215" s="2" t="inlineStr"/>
+      <c r="AD215" s="2" t="inlineStr"/>
+      <c r="AE215" s="2" t="inlineStr"/>
+      <c r="AF215" s="2" t="inlineStr"/>
+      <c r="AG215" s="2" t="inlineStr"/>
+      <c r="AH215" s="2" t="inlineStr"/>
+      <c r="AI215" s="2" t="inlineStr"/>
+      <c r="AJ215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>3f2020ade949451a</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>698fbd14da7d032b3a980c8214767b8eb223167868cd2cea373258eb5e4ac7b4</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>78062</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K216" s="2" t="inlineStr"/>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>0.570381</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="inlineStr"/>
+      <c r="N216" s="2" t="inlineStr"/>
+      <c r="O216" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P216" s="2" t="inlineStr"/>
+      <c r="Q216" s="2" t="inlineStr">
+        <is>
+          <t>0.19015286311787072</t>
+        </is>
+      </c>
+      <c r="R216" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:52.374293Z</t>
+        </is>
+      </c>
+      <c r="S216" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="T216" s="2" t="inlineStr"/>
+      <c r="U216" s="2" t="inlineStr"/>
+      <c r="V216" s="2" t="inlineStr"/>
+      <c r="W216" s="2" t="inlineStr"/>
+      <c r="X216" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y216" s="2" t="inlineStr"/>
+      <c r="Z216" s="2" t="inlineStr"/>
+      <c r="AA216" s="2" t="inlineStr"/>
+      <c r="AB216" s="2" t="inlineStr"/>
+      <c r="AC216" s="2" t="inlineStr"/>
+      <c r="AD216" s="2" t="inlineStr"/>
+      <c r="AE216" s="2" t="inlineStr"/>
+      <c r="AF216" s="2" t="inlineStr"/>
+      <c r="AG216" s="2" t="inlineStr"/>
+      <c r="AH216" s="2" t="inlineStr"/>
+      <c r="AI216" s="2" t="inlineStr"/>
+      <c r="AJ216" s="2" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>c52bf169c3174c6c</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>698fbd14da7d032b3a980c8214767b8eb223167868cd2cea373258eb5e4ac7b4</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>78153</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K217" s="2" t="inlineStr"/>
+      <c r="L217" s="2" t="inlineStr">
+        <is>
+          <t>0.505316</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="inlineStr"/>
+      <c r="N217" s="2" t="inlineStr"/>
+      <c r="O217" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P217" s="2" t="inlineStr"/>
+      <c r="Q217" s="2" t="inlineStr">
+        <is>
+          <t>-0.12431362962962955</t>
+        </is>
+      </c>
+      <c r="R217" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:54.190686Z</t>
+        </is>
+      </c>
+      <c r="S217" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T03:00:00Z</t>
+        </is>
+      </c>
+      <c r="T217" s="2" t="inlineStr"/>
+      <c r="U217" s="2" t="inlineStr"/>
+      <c r="V217" s="2" t="inlineStr"/>
+      <c r="W217" s="2" t="inlineStr"/>
+      <c r="X217" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y217" s="2" t="inlineStr"/>
+      <c r="Z217" s="2" t="inlineStr"/>
+      <c r="AA217" s="2" t="inlineStr"/>
+      <c r="AB217" s="2" t="inlineStr"/>
+      <c r="AC217" s="2" t="inlineStr"/>
+      <c r="AD217" s="2" t="inlineStr"/>
+      <c r="AE217" s="2" t="inlineStr"/>
+      <c r="AF217" s="2" t="inlineStr"/>
+      <c r="AG217" s="2" t="inlineStr"/>
+      <c r="AH217" s="2" t="inlineStr"/>
+      <c r="AI217" s="2" t="inlineStr"/>
+      <c r="AJ217" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ202"/>
+  <autoFilter ref="A1:AJ217"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>